--- a/Stock_Control/INRIPE_Stock_Entry_v1.xlsx
+++ b/Stock_Control/INRIPE_Stock_Entry_v1.xlsx
@@ -36,12 +36,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="dd\-mmm\-yy\ hh:mm"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
-    <numFmt numFmtId="167" formatCode="dd-mmm-yy"/>
-    <numFmt numFmtId="168" formatCode="dd-mmm-yy hh:mm"/>
+    <numFmt numFmtId="167" formatCode="dd\-mmm\-yy"/>
+    <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="169" formatCode="dd-mmm-yy"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -361,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -477,6 +478,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -489,10 +492,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1022,8 +1022,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tblShipment" displayName="tblShipment" ref="A6:I22" headerRowCount="1">
-  <autoFilter ref="A6:I22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tblShipment" displayName="tblShipment" ref="A6:I24" headerRowCount="1">
+  <autoFilter ref="A6:I24"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Shipment No"/>
     <tableColumn id="2" name="Market"/>
@@ -1271,83 +1271,83 @@
   <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col width="2" customWidth="1" style="52" min="1" max="1"/>
-    <col width="16" customWidth="1" style="52" min="2" max="2"/>
-    <col width="13" customWidth="1" style="52" min="3" max="3"/>
-    <col width="46" customWidth="1" style="52" min="4" max="4"/>
-    <col width="34" customWidth="1" style="52" min="5" max="5"/>
+    <col width="2" customWidth="1" style="54" min="1" max="1"/>
+    <col width="16" customWidth="1" style="54" min="2" max="2"/>
+    <col width="13" customWidth="1" style="54" min="3" max="3"/>
+    <col width="46" customWidth="1" style="54" min="4" max="4"/>
+    <col width="34" customWidth="1" style="54" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="52">
+    <row r="1" ht="25.5" customHeight="1" s="54">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>GUIDE</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="52">
+    <row r="2" ht="15" customHeight="1" s="54">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>One page. Read once.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="27.75" customHeight="1" s="52">
-      <c r="B4" s="50" t="inlineStr">
+    <row r="4" ht="27.75" customHeight="1" s="54">
+      <c r="B4" s="52" t="inlineStr">
         <is>
           <t>GOLDEN RULE:   type only what physically happened.   Stock only ever moves through MOVES.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="52">
+    <row r="6" ht="15" customHeight="1" s="54">
       <c r="B6" s="3" t="n"/>
-      <c r="C6" s="53" t="inlineStr">
+      <c r="C6" s="55" t="inlineStr">
         <is>
           <t>BLUE  =  you type here</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="52">
+    <row r="7" ht="15" customHeight="1" s="54">
       <c r="B7" s="4" t="n"/>
-      <c r="C7" s="53" t="inlineStr">
+      <c r="C7" s="55" t="inlineStr">
         <is>
           <t>GREY  =  the workbook works it out</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="52">
+    <row r="8" ht="15" customHeight="1" s="54">
       <c r="B8" s="5" t="n"/>
-      <c r="C8" s="53" t="inlineStr">
+      <c r="C8" s="55" t="inlineStr">
         <is>
           <t>YELLOW  =  a setting you may change</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="52">
+    <row r="9" ht="15" customHeight="1" s="54">
       <c r="B9" s="6" t="n"/>
-      <c r="C9" s="53" t="inlineStr">
+      <c r="C9" s="55" t="inlineStr">
         <is>
           <t>RED  =  fix this row</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="52">
+    <row r="10" ht="15" customHeight="1" s="54">
       <c r="B10" s="7" t="n"/>
-      <c r="C10" s="53" t="inlineStr">
+      <c r="C10" s="55" t="inlineStr">
         <is>
           <t>GREEN  =  stock coming IN</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="52">
+    <row r="11" ht="15" customHeight="1" s="54">
       <c r="B11" s="8" t="n"/>
-      <c r="C11" s="53" t="inlineStr">
+      <c r="C11" s="55" t="inlineStr">
         <is>
           <t>PINK  =  stock going OUT</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" s="52">
+    <row r="14" ht="24" customHeight="1" s="54">
       <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Sheet</t>
@@ -1364,211 +1364,211 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="52">
+    <row r="15" ht="15" customHeight="1" s="54">
       <c r="B15" s="10" t="inlineStr">
         <is>
           <t>SHIPMENTS</t>
         </is>
       </c>
-      <c r="C15" s="51" t="inlineStr">
+      <c r="C15" s="53" t="inlineStr">
         <is>
           <t>Per shipment</t>
         </is>
       </c>
-      <c r="D15" s="51" t="inlineStr">
+      <c r="D15" s="53" t="inlineStr">
         <is>
           <t>6 fields: Shipment No, Market, Arrival Date, Source, Item Name, Shipped Qty</t>
         </is>
       </c>
-      <c r="E15" s="54" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="52">
+      <c r="E15" s="56" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="54">
       <c r="B16" s="12" t="inlineStr">
         <is>
           <t>MOVES</t>
         </is>
       </c>
-      <c r="C16" s="49" t="inlineStr">
+      <c r="C16" s="51" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="D16" s="49" t="inlineStr">
+      <c r="D16" s="51" t="inlineStr">
         <is>
           <t>6 fields at most. Pick the Movement and it tells you which ones.</t>
         </is>
       </c>
-      <c r="E16" s="54" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="52">
+      <c r="E16" s="56" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="54">
       <c r="B17" s="10" t="inlineStr">
         <is>
           <t>COUNT</t>
         </is>
       </c>
-      <c r="C17" s="51" t="inlineStr">
+      <c r="C17" s="53" t="inlineStr">
         <is>
           <t>Weekly</t>
         </is>
       </c>
-      <c r="D17" s="51" t="inlineStr">
+      <c r="D17" s="53" t="inlineStr">
         <is>
           <t>4 fields: Date, Shipment No, Item Name, Physical Qty</t>
         </is>
       </c>
-      <c r="E17" s="54" t="n"/>
-    </row>
-    <row r="18" ht="21.75" customHeight="1" s="52">
+      <c r="E17" s="56" t="n"/>
+    </row>
+    <row r="18" ht="21.75" customHeight="1" s="54">
       <c r="B18" s="12" t="inlineStr">
         <is>
           <t>DISPATCH</t>
         </is>
       </c>
-      <c r="C18" s="49" t="inlineStr">
+      <c r="C18" s="51" t="inlineStr">
         <is>
           <t>Never - automatic</t>
         </is>
       </c>
-      <c r="D18" s="49" t="inlineStr">
+      <c r="D18" s="51" t="inlineStr">
         <is>
           <t>Which orders took which boxes. The dashboard writes it.</t>
         </is>
       </c>
-      <c r="E18" s="54" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="52">
+      <c r="E18" s="56" t="n"/>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="54">
       <c r="B19" s="10" t="inlineStr">
         <is>
           <t>MASTER</t>
         </is>
       </c>
-      <c r="C19" s="51" t="inlineStr">
+      <c r="C19" s="53" t="inlineStr">
         <is>
           <t>Rarely</t>
         </is>
       </c>
-      <c r="D19" s="51" t="inlineStr">
+      <c r="D19" s="53" t="inlineStr">
         <is>
           <t>Items, courier, reasons, movements, settings</t>
         </is>
       </c>
-      <c r="E19" s="54" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="52">
+      <c r="E19" s="56" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="54">
       <c r="B22" s="14" t="inlineStr">
         <is>
           <t>Your daily routine</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="52">
+    <row r="23" ht="15" customHeight="1" s="54">
       <c r="B23" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   1.  New shipment landed? Add its lines on SHIPMENTS first - one row per item.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="52">
+    <row r="24" ht="15" customHeight="1" s="54">
       <c r="B24" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   2.  Open MOVES. Type the Date and Shipment No, then pick the Movement.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="52">
+    <row r="25" ht="15" customHeight="1" s="54">
       <c r="B25" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   3.  Read the 'What to fill' column. It names every field that movement needs - fill only those.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="52">
+    <row r="26" ht="15" customHeight="1" s="54">
       <c r="B26" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   4.  Quantities go in the In column or the Out column, never both. The column tells you which.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="52">
+    <row r="27" ht="15" customHeight="1" s="54">
       <c r="B27" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   5.  Check the last column shows OK on every new row. Save the file.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="52">
+    <row r="28" ht="15" customHeight="1" s="54">
       <c r="B28" s="15" t="n"/>
     </row>
-    <row r="29" ht="15" customHeight="1" s="52">
+    <row r="29" ht="15" customHeight="1" s="54">
       <c r="B29" s="14" t="inlineStr">
         <is>
           <t>Made a mistake?</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="52">
+    <row r="30" ht="15" customHeight="1" s="54">
       <c r="B30" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   Set Void to Yes on that row. It is ignored everywhere and stays visible for audit. Never delete a row.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="52">
+    <row r="31" ht="15" customHeight="1" s="54">
       <c r="B31" s="15" t="n"/>
     </row>
-    <row r="32" ht="15" customHeight="1" s="52">
+    <row r="32" ht="15" customHeight="1" s="54">
       <c r="B32" s="14" t="inlineStr">
         <is>
           <t>Rules that never change</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="52">
+    <row r="33" ht="15" customHeight="1" s="54">
       <c r="B33" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   Items are tracked inside the store. Once boxes go to the courier, quantities are tracked by shipment.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="52">
+    <row r="34" ht="15" customHeight="1" s="54">
       <c r="B34" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   Returns: enter Returned (no item), then split it the same day into Return to Saleable and Return to Scrap.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="52">
+    <row r="35" ht="15" customHeight="1" s="54">
       <c r="B35" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   Orders are counts, never order numbers. Order numbers appear only on DISPATCH, written automatically.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="52">
+    <row r="36" ht="15" customHeight="1" s="54">
       <c r="B36" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   A physical count never changes stock. Post a Count Adjustment in MOVES with a reason instead.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="52">
+    <row r="37" ht="15" customHeight="1" s="54">
       <c r="B37" s="15" t="n"/>
     </row>
-    <row r="38" ht="15" customHeight="1" s="52">
+    <row r="38" ht="15" customHeight="1" s="54">
       <c r="B38" s="14" t="inlineStr">
         <is>
           <t>Growing this file</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="52">
+    <row r="39" ht="15" customHeight="1" s="54">
       <c r="B39" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   New item, courier or reason  -&gt;  add a row on MASTER.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" s="52">
+    <row r="40" ht="15" customHeight="1" s="54">
       <c r="B40" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   New kind of movement  -&gt;  add a row to the Movement Types table on MASTER. Nothing else changes.</t>
@@ -1602,59 +1602,59 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB31"/>
+  <dimension ref="A1:AB32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col width="2" customWidth="1" style="52" min="1" max="1"/>
-    <col width="49.5703125" customWidth="1" style="52" min="2" max="2"/>
-    <col width="24" customWidth="1" style="52" min="3" max="3"/>
-    <col width="9" customWidth="1" style="52" min="4" max="4"/>
-    <col width="2" customWidth="1" style="52" min="5" max="5"/>
-    <col width="10" customWidth="1" style="52" min="6" max="6"/>
-    <col width="8" customWidth="1" style="52" min="7" max="7"/>
-    <col width="2" customWidth="1" style="52" min="8" max="8"/>
-    <col width="12" customWidth="1" style="52" min="9" max="9"/>
-    <col width="9" customWidth="1" style="52" min="10" max="10"/>
-    <col width="8" customWidth="1" style="52" min="11" max="11"/>
-    <col width="2" customWidth="1" style="52" min="12" max="12"/>
-    <col width="22" customWidth="1" style="52" min="13" max="13"/>
-    <col width="10" customWidth="1" style="52" min="14" max="14"/>
-    <col width="2" customWidth="1" style="52" min="15" max="15"/>
-    <col width="25" customWidth="1" style="52" min="16" max="16"/>
-    <col width="30" customWidth="1" style="52" min="17" max="17"/>
-    <col width="7" customWidth="1" style="52" min="18" max="19"/>
-    <col width="9" customWidth="1" style="52" min="20" max="20"/>
-    <col width="8" customWidth="1" style="52" min="21" max="22"/>
-    <col width="7" customWidth="1" style="52" min="23" max="23"/>
-    <col width="2" customWidth="1" style="52" min="24" max="24"/>
-    <col width="16" customWidth="1" style="52" min="25" max="25"/>
-    <col width="10" customWidth="1" style="52" min="26" max="26"/>
-    <col width="9" customWidth="1" style="52" min="27" max="27"/>
-    <col width="8" customWidth="1" style="52" min="28" max="28"/>
+    <col width="2" customWidth="1" style="54" min="1" max="1"/>
+    <col width="49.5703125" customWidth="1" style="54" min="2" max="2"/>
+    <col width="24" customWidth="1" style="54" min="3" max="3"/>
+    <col width="9" customWidth="1" style="54" min="4" max="4"/>
+    <col width="2" customWidth="1" style="54" min="5" max="5"/>
+    <col width="10" customWidth="1" style="54" min="6" max="6"/>
+    <col width="8" customWidth="1" style="54" min="7" max="7"/>
+    <col width="2" customWidth="1" style="54" min="8" max="8"/>
+    <col width="12" customWidth="1" style="54" min="9" max="9"/>
+    <col width="9" customWidth="1" style="54" min="10" max="10"/>
+    <col width="8" customWidth="1" style="54" min="11" max="11"/>
+    <col width="2" customWidth="1" style="54" min="12" max="12"/>
+    <col width="22" customWidth="1" style="54" min="13" max="13"/>
+    <col width="10" customWidth="1" style="54" min="14" max="14"/>
+    <col width="2" customWidth="1" style="54" min="15" max="15"/>
+    <col width="25" customWidth="1" style="54" min="16" max="16"/>
+    <col width="30" customWidth="1" style="54" min="17" max="17"/>
+    <col width="7" customWidth="1" style="54" min="18" max="19"/>
+    <col width="9" customWidth="1" style="54" min="20" max="20"/>
+    <col width="8" customWidth="1" style="54" min="21" max="22"/>
+    <col width="7" customWidth="1" style="54" min="23" max="23"/>
+    <col width="2" customWidth="1" style="54" min="24" max="24"/>
+    <col width="16" customWidth="1" style="54" min="25" max="25"/>
+    <col width="10" customWidth="1" style="54" min="26" max="26"/>
+    <col width="9" customWidth="1" style="54" min="27" max="27"/>
+    <col width="8" customWidth="1" style="54" min="28" max="28"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="52">
+    <row r="1" ht="25.5" customHeight="1" s="54">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>MASTER  -  standards</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="52">
+    <row r="2" ht="15" customHeight="1" s="54">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Set once. Everything else reads from here.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1" s="52">
+    <row r="4" ht="15.75" customHeight="1" s="54">
       <c r="B4" s="16" t="inlineStr">
         <is>
           <t>SETTINGS</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="52">
+    <row r="5" ht="15" customHeight="1" s="54">
       <c r="B5" s="17" t="inlineStr">
         <is>
           <t>As-Of Date</t>
@@ -1664,7 +1664,7 @@
         <v>46258</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="52">
+    <row r="6" ht="15" customHeight="1" s="54">
       <c r="B6" s="17" t="inlineStr">
         <is>
           <t>Courier holding limit (days)</t>
@@ -1674,7 +1674,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="52">
+    <row r="7" ht="15" customHeight="1" s="54">
       <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Shipment clearance target (days)</t>
@@ -1684,7 +1684,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="52">
+    <row r="8" ht="15" customHeight="1" s="54">
       <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Loss % target</t>
@@ -1694,7 +1694,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="52">
+    <row r="9" ht="15" customHeight="1" s="54">
       <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Count variance tolerance</t>
@@ -1704,7 +1704,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="52">
+    <row r="10" ht="15" customHeight="1" s="54">
       <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Version</t>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="52">
+    <row r="12" ht="15" customHeight="1" s="54">
       <c r="B12" s="22" t="inlineStr">
         <is>
           <t>Yellow = the only cells you change here.  Holding limit 99 = no limit.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15.75" customHeight="1" s="52">
+    <row r="14" ht="15.75" customHeight="1" s="54">
       <c r="B14" s="16" t="inlineStr">
         <is>
           <t>MASTER TABLES</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" s="52">
+    <row r="15" ht="30" customHeight="1" s="54">
       <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Item Name</t>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="52">
+    <row r="16" ht="15" customHeight="1" s="54">
       <c r="B16" s="24" t="inlineStr">
         <is>
           <t>Mango Fas</t>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="52">
+    <row r="17" ht="15" customHeight="1" s="54">
       <c r="B17" s="24" t="inlineStr">
         <is>
           <t>Mango Owais</t>
@@ -2066,7 +2066,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="52">
+    <row r="18" ht="15" customHeight="1" s="54">
       <c r="B18" s="24" t="inlineStr">
         <is>
           <t>Fig Barshomi</t>
@@ -2178,7 +2178,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="52">
+    <row r="19" ht="15" customHeight="1" s="54">
       <c r="B19" s="24" t="inlineStr">
         <is>
           <t>Guava Banati</t>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="52">
+    <row r="20" ht="15" customHeight="1" s="54">
       <c r="B20" s="24" t="inlineStr">
         <is>
           <t>Mango White Sugar</t>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="52">
+    <row r="21" ht="15" customHeight="1" s="54">
       <c r="B21" s="24" t="inlineStr">
         <is>
           <t>Dates Barhi</t>
@@ -2444,7 +2444,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="52">
+    <row r="22" ht="15" customHeight="1" s="54">
       <c r="B22" s="24" t="inlineStr">
         <is>
           <t>Mango Trio Box</t>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="52">
+    <row r="23" ht="15" customHeight="1" s="54">
       <c r="B23" s="24" t="inlineStr">
         <is>
           <t>Mango Fons</t>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="52">
+    <row r="24" ht="15" customHeight="1" s="54">
       <c r="B24" s="24" t="inlineStr">
         <is>
           <t>Grapes Banati</t>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="52">
+    <row r="25" ht="15" customHeight="1" s="54">
       <c r="B25" s="24" t="inlineStr">
         <is>
           <t>Grapes Red</t>
@@ -2685,7 +2685,7 @@
       <c r="V25" s="24" t="n"/>
       <c r="W25" s="24" t="n"/>
     </row>
-    <row r="26" ht="15" customHeight="1" s="52">
+    <row r="26" ht="15" customHeight="1" s="54">
       <c r="B26" s="24" t="inlineStr">
         <is>
           <t>Mango Sediqa</t>
@@ -2720,7 +2720,7 @@
       <c r="V26" s="24" t="n"/>
       <c r="W26" s="24" t="n"/>
     </row>
-    <row r="27" ht="15" customHeight="1" s="52">
+    <row r="27" ht="15" customHeight="1" s="54">
       <c r="B27" s="24" t="inlineStr">
         <is>
           <t>Pear Banati</t>
@@ -2755,7 +2755,7 @@
       <c r="V27" s="24" t="n"/>
       <c r="W27" s="24" t="n"/>
     </row>
-    <row r="28" ht="15" customHeight="1" s="52">
+    <row r="28" ht="15" customHeight="1" s="54">
       <c r="B28" s="24" t="inlineStr">
         <is>
           <t>Cantaloupe</t>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="52">
+    <row r="29" ht="15" customHeight="1" s="54">
       <c r="B29" s="24" t="inlineStr">
         <is>
           <t>Mango Naomi</t>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="52">
+    <row r="30" ht="15" customHeight="1" s="54">
       <c r="B30" s="24" t="inlineStr">
         <is>
           <t>Mango Zebda</t>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="52">
+    <row r="31" ht="15" customHeight="1" s="54">
       <c r="B31" s="24" t="inlineStr">
         <is>
           <t>Mango Timour</t>
@@ -2858,6 +2858,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -2879,42 +2880,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" style="52" min="1" max="1"/>
-    <col width="9" customWidth="1" style="52" min="2" max="2"/>
-    <col width="18.42578125" bestFit="1" customWidth="1" style="52" min="3" max="3"/>
-    <col width="9" customWidth="1" style="52" min="4" max="4"/>
-    <col width="20" customWidth="1" style="52" min="5" max="5"/>
-    <col width="12" customWidth="1" style="52" min="6" max="6"/>
-    <col width="20" customWidth="1" style="52" min="7" max="7"/>
-    <col width="23.140625" customWidth="1" style="52" min="8" max="8"/>
-    <col width="26" customWidth="1" style="52" min="9" max="9"/>
+    <col width="13" customWidth="1" style="54" min="1" max="1"/>
+    <col width="9" customWidth="1" style="54" min="2" max="2"/>
+    <col width="18.42578125" bestFit="1" customWidth="1" style="54" min="3" max="3"/>
+    <col width="9" customWidth="1" style="54" min="4" max="4"/>
+    <col width="20" customWidth="1" style="54" min="5" max="5"/>
+    <col width="12" customWidth="1" style="54" min="6" max="6"/>
+    <col width="20" customWidth="1" style="54" min="7" max="7"/>
+    <col width="23.140625" customWidth="1" style="54" min="8" max="8"/>
+    <col width="26" customWidth="1" style="54" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="52">
+    <row r="1" ht="25.5" customHeight="1" s="54">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SHIPMENTS  -  what arrived</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="52">
+    <row r="2" ht="15" customHeight="1" s="54">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>One row per shipment and item. Filled once, when the shipment lands.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="52">
+    <row r="4" ht="15" customHeight="1" s="54">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>BLUE = you type it.   GREY = the workbook works it out.   RED = fix that row.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="31.5" customHeight="1" s="52">
+    <row r="6" ht="31.5" customHeight="1" s="54">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Shipment No</t>
@@ -2961,7 +2962,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="52">
+    <row r="7" ht="15" customHeight="1" s="54">
       <c r="A7" t="inlineStr">
         <is>
           <t>Q-26-001</t>
@@ -2999,7 +3000,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="52">
+    <row r="8" ht="15" customHeight="1" s="54">
       <c r="A8" t="inlineStr">
         <is>
           <t>Q-26-001</t>
@@ -3037,7 +3038,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="52">
+    <row r="9" ht="15" customHeight="1" s="54">
       <c r="A9" t="inlineStr">
         <is>
           <t>Q-26-001</t>
@@ -3075,7 +3076,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="52">
+    <row r="10" ht="15" customHeight="1" s="54">
       <c r="A10" t="inlineStr">
         <is>
           <t>Q-26-001</t>
@@ -3113,7 +3114,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="52">
+    <row r="11" ht="15" customHeight="1" s="54">
       <c r="A11" t="inlineStr">
         <is>
           <t>Q-26-001</t>
@@ -3151,7 +3152,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="52">
+    <row r="12" ht="15" customHeight="1" s="54">
       <c r="A12" t="inlineStr">
         <is>
           <t>Q-26-001</t>
@@ -3189,7 +3190,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="52">
+    <row r="13" ht="15" customHeight="1" s="54">
       <c r="A13" t="inlineStr">
         <is>
           <t>Q-26-001</t>
@@ -3227,7 +3228,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="52">
+    <row r="14" ht="15" customHeight="1" s="54">
       <c r="A14" t="inlineStr">
         <is>
           <t>Q-26-001</t>
@@ -3265,7 +3266,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="52">
+    <row r="15" ht="15" customHeight="1" s="54">
       <c r="A15" t="inlineStr">
         <is>
           <t>Q-26-001</t>
@@ -3303,7 +3304,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="52">
+    <row r="16" ht="15" customHeight="1" s="54">
       <c r="A16" t="inlineStr">
         <is>
           <t>Q-26-001</t>
@@ -3341,7 +3342,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="52">
+    <row r="17" ht="15" customHeight="1" s="54">
       <c r="A17" t="inlineStr">
         <is>
           <t>Q-26-001</t>
@@ -3379,7 +3380,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="52">
+    <row r="18" ht="15" customHeight="1" s="54">
       <c r="A18" t="inlineStr">
         <is>
           <t>Q-26-001</t>
@@ -3417,7 +3418,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="52">
+    <row r="19" ht="15" customHeight="1" s="54">
       <c r="A19" t="inlineStr">
         <is>
           <t>Q-26-001</t>
@@ -3455,7 +3456,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="52">
+    <row r="20" ht="15" customHeight="1" s="54">
       <c r="A20" t="inlineStr">
         <is>
           <t>Q-26-001</t>
@@ -3493,7 +3494,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="52">
+    <row r="21" ht="15" customHeight="1" s="54">
       <c r="A21" t="inlineStr">
         <is>
           <t>Q-26-001</t>
@@ -3531,7 +3532,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="52">
+    <row r="22" ht="15" customHeight="1" s="54">
       <c r="A22" t="inlineStr">
         <is>
           <t>Q-26-001</t>
@@ -3569,119 +3570,193 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="52"/>
-    <row r="24" ht="15" customHeight="1" s="52"/>
-    <row r="25" ht="15" customHeight="1" s="52"/>
-    <row r="26" ht="15" customHeight="1" s="52"/>
-    <row r="27" ht="15" customHeight="1" s="52"/>
-    <row r="28" ht="15" customHeight="1" s="52"/>
-    <row r="29" ht="15" customHeight="1" s="52"/>
-    <row r="30" ht="15" customHeight="1" s="52"/>
-    <row r="31" ht="15" customHeight="1" s="52"/>
-    <row r="32" ht="15" customHeight="1" s="52"/>
-    <row r="33" ht="15" customHeight="1" s="52"/>
-    <row r="34" ht="15" customHeight="1" s="52"/>
-    <row r="35" ht="15" customHeight="1" s="52"/>
-    <row r="36" ht="15" customHeight="1" s="52"/>
-    <row r="37" ht="15" customHeight="1" s="52"/>
-    <row r="38" ht="15" customHeight="1" s="52"/>
-    <row r="39" ht="15" customHeight="1" s="52"/>
-    <row r="40" ht="15" customHeight="1" s="52"/>
-    <row r="41" ht="15" customHeight="1" s="52"/>
-    <row r="42" ht="15" customHeight="1" s="52"/>
-    <row r="43" ht="15" customHeight="1" s="52"/>
-    <row r="44" ht="15" customHeight="1" s="52"/>
-    <row r="45" ht="15" customHeight="1" s="52"/>
-    <row r="46" ht="15" customHeight="1" s="52"/>
-    <row r="47" ht="15" customHeight="1" s="52"/>
-    <row r="48" ht="15" customHeight="1" s="52"/>
-    <row r="49" ht="15" customHeight="1" s="52"/>
-    <row r="50" ht="15" customHeight="1" s="52"/>
-    <row r="51" ht="15" customHeight="1" s="52"/>
-    <row r="52" ht="15" customHeight="1" s="52"/>
-    <row r="53" ht="15" customHeight="1" s="52"/>
-    <row r="54" ht="15" customHeight="1" s="52"/>
-    <row r="55" ht="15" customHeight="1" s="52"/>
-    <row r="56" ht="15" customHeight="1" s="52"/>
-    <row r="57" ht="15" customHeight="1" s="52"/>
-    <row r="58" ht="15" customHeight="1" s="52"/>
-    <row r="59" ht="15" customHeight="1" s="52"/>
-    <row r="60" ht="15" customHeight="1" s="52"/>
-    <row r="61" ht="15" customHeight="1" s="52"/>
-    <row r="62" ht="15" customHeight="1" s="52"/>
-    <row r="63" ht="15" customHeight="1" s="52"/>
-    <row r="64" ht="15" customHeight="1" s="52"/>
-    <row r="65" ht="15" customHeight="1" s="52"/>
-    <row r="66" ht="15" customHeight="1" s="52"/>
-    <row r="67" ht="15" customHeight="1" s="52"/>
-    <row r="68" ht="15" customHeight="1" s="52"/>
-    <row r="69" ht="15" customHeight="1" s="52"/>
-    <row r="70" ht="15" customHeight="1" s="52"/>
-    <row r="71" ht="15" customHeight="1" s="52"/>
-    <row r="72" ht="15" customHeight="1" s="52"/>
-    <row r="73" ht="15" customHeight="1" s="52"/>
-    <row r="74" ht="15" customHeight="1" s="52"/>
-    <row r="75" ht="15" customHeight="1" s="52"/>
-    <row r="76" ht="15" customHeight="1" s="52"/>
-    <row r="77" ht="15" customHeight="1" s="52"/>
-    <row r="78" ht="15" customHeight="1" s="52"/>
-    <row r="79" ht="15" customHeight="1" s="52"/>
-    <row r="80" ht="15" customHeight="1" s="52"/>
-    <row r="81" ht="15" customHeight="1" s="52"/>
-    <row r="82" ht="15" customHeight="1" s="52"/>
-    <row r="83" ht="15" customHeight="1" s="52"/>
-    <row r="84" ht="15" customHeight="1" s="52"/>
-    <row r="85" ht="15" customHeight="1" s="52"/>
-    <row r="86" ht="15" customHeight="1" s="52"/>
-    <row r="87" ht="15" customHeight="1" s="52"/>
-    <row r="88" ht="15" customHeight="1" s="52"/>
-    <row r="89" ht="15" customHeight="1" s="52"/>
-    <row r="90" ht="15" customHeight="1" s="52"/>
-    <row r="91" ht="15" customHeight="1" s="52"/>
-    <row r="92" ht="15" customHeight="1" s="52"/>
-    <row r="93" ht="15" customHeight="1" s="52"/>
-    <row r="94" ht="15" customHeight="1" s="52"/>
-    <row r="95" ht="15" customHeight="1" s="52"/>
-    <row r="96" ht="15" customHeight="1" s="52"/>
-    <row r="97" ht="15" customHeight="1" s="52"/>
-    <row r="98" ht="15" customHeight="1" s="52"/>
-    <row r="99" ht="15" customHeight="1" s="52"/>
-    <row r="100" ht="15" customHeight="1" s="52"/>
-    <row r="101" ht="15" customHeight="1" s="52"/>
-    <row r="102" ht="15" customHeight="1" s="52"/>
-    <row r="103" ht="15" customHeight="1" s="52"/>
-    <row r="104" ht="15" customHeight="1" s="52"/>
-    <row r="105" ht="15" customHeight="1" s="52"/>
-    <row r="106" ht="15" customHeight="1" s="52"/>
-    <row r="107" ht="15" customHeight="1" s="52"/>
-    <row r="108" ht="15" customHeight="1" s="52"/>
-    <row r="109" ht="15" customHeight="1" s="52"/>
-    <row r="110" ht="15" customHeight="1" s="52"/>
-    <row r="111" ht="15" customHeight="1" s="52"/>
-    <row r="112" ht="15" customHeight="1" s="52"/>
-    <row r="113" ht="15" customHeight="1" s="52"/>
-    <row r="114" ht="15" customHeight="1" s="52"/>
-    <row r="115" ht="15" customHeight="1" s="52"/>
-    <row r="116" ht="15" customHeight="1" s="52"/>
-    <row r="117" ht="15" customHeight="1" s="52"/>
-    <row r="118" ht="15" customHeight="1" s="52"/>
-    <row r="119" ht="15" customHeight="1" s="52"/>
-    <row r="120" ht="15" customHeight="1" s="52"/>
-    <row r="121" ht="15" customHeight="1" s="52"/>
-    <row r="122" ht="15" customHeight="1" s="52"/>
-    <row r="123" ht="15" customHeight="1" s="52"/>
-    <row r="124" ht="15" customHeight="1" s="52"/>
-    <row r="125" ht="15" customHeight="1" s="52"/>
-    <row r="126" ht="15" customHeight="1" s="52"/>
-    <row r="127" ht="15" customHeight="1" s="52"/>
-    <row r="128" ht="15" customHeight="1" s="52"/>
-    <row r="129" ht="15" customHeight="1" s="52"/>
-    <row r="130" ht="15" customHeight="1" s="52"/>
-    <row r="131" ht="15" customHeight="1" s="52"/>
-    <row r="132" ht="15" customHeight="1" s="52"/>
-    <row r="133" ht="15" customHeight="1" s="52"/>
-    <row r="134" ht="15" customHeight="1" s="52"/>
-    <row r="135" ht="15" customHeight="1" s="52"/>
+    <row r="23" ht="15" customHeight="1" s="54">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Q-26-002</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="C23" s="57" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Grapes Banati</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>EG-FG-GRP-01-02-01-01</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="54">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Q-26-002</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="C24" s="57" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Fig Barshomi</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>EG-FG-FIG-01-02-01-01</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="54"/>
+    <row r="26" ht="15" customHeight="1" s="54"/>
+    <row r="27" ht="15" customHeight="1" s="54"/>
+    <row r="28" ht="15" customHeight="1" s="54"/>
+    <row r="29" ht="15" customHeight="1" s="54"/>
+    <row r="30" ht="15" customHeight="1" s="54"/>
+    <row r="31" ht="15" customHeight="1" s="54"/>
+    <row r="32" ht="15" customHeight="1" s="54"/>
+    <row r="33" ht="15" customHeight="1" s="54"/>
+    <row r="34" ht="15" customHeight="1" s="54"/>
+    <row r="35" ht="15" customHeight="1" s="54"/>
+    <row r="36" ht="15" customHeight="1" s="54"/>
+    <row r="37" ht="15" customHeight="1" s="54"/>
+    <row r="38" ht="15" customHeight="1" s="54"/>
+    <row r="39" ht="15" customHeight="1" s="54"/>
+    <row r="40" ht="15" customHeight="1" s="54"/>
+    <row r="41" ht="15" customHeight="1" s="54"/>
+    <row r="42" ht="15" customHeight="1" s="54"/>
+    <row r="43" ht="15" customHeight="1" s="54"/>
+    <row r="44" ht="15" customHeight="1" s="54"/>
+    <row r="45" ht="15" customHeight="1" s="54"/>
+    <row r="46" ht="15" customHeight="1" s="54"/>
+    <row r="47" ht="15" customHeight="1" s="54"/>
+    <row r="48" ht="15" customHeight="1" s="54"/>
+    <row r="49" ht="15" customHeight="1" s="54"/>
+    <row r="50" ht="15" customHeight="1" s="54"/>
+    <row r="51" ht="15" customHeight="1" s="54"/>
+    <row r="52" ht="15" customHeight="1" s="54"/>
+    <row r="53" ht="15" customHeight="1" s="54"/>
+    <row r="54" ht="15" customHeight="1" s="54"/>
+    <row r="55" ht="15" customHeight="1" s="54"/>
+    <row r="56" ht="15" customHeight="1" s="54"/>
+    <row r="57" ht="15" customHeight="1" s="54"/>
+    <row r="58" ht="15" customHeight="1" s="54"/>
+    <row r="59" ht="15" customHeight="1" s="54"/>
+    <row r="60" ht="15" customHeight="1" s="54"/>
+    <row r="61" ht="15" customHeight="1" s="54"/>
+    <row r="62" ht="15" customHeight="1" s="54"/>
+    <row r="63" ht="15" customHeight="1" s="54"/>
+    <row r="64" ht="15" customHeight="1" s="54"/>
+    <row r="65" ht="15" customHeight="1" s="54"/>
+    <row r="66" ht="15" customHeight="1" s="54"/>
+    <row r="67" ht="15" customHeight="1" s="54"/>
+    <row r="68" ht="15" customHeight="1" s="54"/>
+    <row r="69" ht="15" customHeight="1" s="54"/>
+    <row r="70" ht="15" customHeight="1" s="54"/>
+    <row r="71" ht="15" customHeight="1" s="54"/>
+    <row r="72" ht="15" customHeight="1" s="54"/>
+    <row r="73" ht="15" customHeight="1" s="54"/>
+    <row r="74" ht="15" customHeight="1" s="54"/>
+    <row r="75" ht="15" customHeight="1" s="54"/>
+    <row r="76" ht="15" customHeight="1" s="54"/>
+    <row r="77" ht="15" customHeight="1" s="54"/>
+    <row r="78" ht="15" customHeight="1" s="54"/>
+    <row r="79" ht="15" customHeight="1" s="54"/>
+    <row r="80" ht="15" customHeight="1" s="54"/>
+    <row r="81" ht="15" customHeight="1" s="54"/>
+    <row r="82" ht="15" customHeight="1" s="54"/>
+    <row r="83" ht="15" customHeight="1" s="54"/>
+    <row r="84" ht="15" customHeight="1" s="54"/>
+    <row r="85" ht="15" customHeight="1" s="54"/>
+    <row r="86" ht="15" customHeight="1" s="54"/>
+    <row r="87" ht="15" customHeight="1" s="54"/>
+    <row r="88" ht="15" customHeight="1" s="54"/>
+    <row r="89" ht="15" customHeight="1" s="54"/>
+    <row r="90" ht="15" customHeight="1" s="54"/>
+    <row r="91" ht="15" customHeight="1" s="54"/>
+    <row r="92" ht="15" customHeight="1" s="54"/>
+    <row r="93" ht="15" customHeight="1" s="54"/>
+    <row r="94" ht="15" customHeight="1" s="54"/>
+    <row r="95" ht="15" customHeight="1" s="54"/>
+    <row r="96" ht="15" customHeight="1" s="54"/>
+    <row r="97" ht="15" customHeight="1" s="54"/>
+    <row r="98" ht="15" customHeight="1" s="54"/>
+    <row r="99" ht="15" customHeight="1" s="54"/>
+    <row r="100" ht="15" customHeight="1" s="54"/>
+    <row r="101" ht="15" customHeight="1" s="54"/>
+    <row r="102" ht="15" customHeight="1" s="54"/>
+    <row r="103" ht="15" customHeight="1" s="54"/>
+    <row r="104" ht="15" customHeight="1" s="54"/>
+    <row r="105" ht="15" customHeight="1" s="54"/>
+    <row r="106" ht="15" customHeight="1" s="54"/>
+    <row r="107" ht="15" customHeight="1" s="54"/>
+    <row r="108" ht="15" customHeight="1" s="54"/>
+    <row r="109" ht="15" customHeight="1" s="54"/>
+    <row r="110" ht="15" customHeight="1" s="54"/>
+    <row r="111" ht="15" customHeight="1" s="54"/>
+    <row r="112" ht="15" customHeight="1" s="54"/>
+    <row r="113" ht="15" customHeight="1" s="54"/>
+    <row r="114" ht="15" customHeight="1" s="54"/>
+    <row r="115" ht="15" customHeight="1" s="54"/>
+    <row r="116" ht="15" customHeight="1" s="54"/>
+    <row r="117" ht="15" customHeight="1" s="54"/>
+    <row r="118" ht="15" customHeight="1" s="54"/>
+    <row r="119" ht="15" customHeight="1" s="54"/>
+    <row r="120" ht="15" customHeight="1" s="54"/>
+    <row r="121" ht="15" customHeight="1" s="54"/>
+    <row r="122" ht="15" customHeight="1" s="54"/>
+    <row r="123" ht="15" customHeight="1" s="54"/>
+    <row r="124" ht="15" customHeight="1" s="54"/>
+    <row r="125" ht="15" customHeight="1" s="54"/>
+    <row r="126" ht="15" customHeight="1" s="54"/>
+    <row r="127" ht="15" customHeight="1" s="54"/>
+    <row r="128" ht="15" customHeight="1" s="54"/>
+    <row r="129" ht="15" customHeight="1" s="54"/>
+    <row r="130" ht="15" customHeight="1" s="54"/>
+    <row r="131" ht="15" customHeight="1" s="54"/>
+    <row r="132" ht="15" customHeight="1" s="54"/>
+    <row r="133" ht="15" customHeight="1" s="54"/>
+    <row r="134" ht="15" customHeight="1" s="54"/>
+    <row r="135" ht="15" customHeight="1" s="54"/>
   </sheetData>
   <conditionalFormatting sqref="I7:I9000">
     <cfRule type="expression" priority="2" dxfId="0">
@@ -3720,47 +3795,47 @@
   <dimension ref="A1:S31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" style="52" min="1" max="1"/>
-    <col width="12" customWidth="1" style="52" min="2" max="2"/>
-    <col width="24.85546875" customWidth="1" style="52" min="3" max="3"/>
-    <col width="34" customWidth="1" style="52" min="4" max="4"/>
-    <col width="20" customWidth="1" style="52" min="5" max="5"/>
-    <col width="8" customWidth="1" style="52" min="6" max="7"/>
-    <col width="8.42578125" customWidth="1" style="52" min="8" max="8"/>
-    <col width="13" customWidth="1" style="52" min="9" max="9"/>
-    <col width="19" customWidth="1" style="52" min="10" max="10"/>
-    <col width="18" customWidth="1" style="52" min="11" max="11"/>
-    <col width="7" customWidth="1" style="52" min="12" max="12"/>
-    <col width="23" customWidth="1" style="52" min="13" max="13"/>
-    <col width="9" customWidth="1" style="52" min="14" max="14"/>
-    <col width="7" customWidth="1" style="52" min="15" max="15"/>
-    <col width="17" customWidth="1" style="52" min="16" max="16"/>
-    <col width="13" customWidth="1" style="52" min="17" max="17"/>
-    <col width="17" customWidth="1" style="52" min="18" max="18"/>
+    <col width="11" customWidth="1" style="54" min="1" max="1"/>
+    <col width="12" customWidth="1" style="54" min="2" max="2"/>
+    <col width="24.85546875" customWidth="1" style="54" min="3" max="3"/>
+    <col width="34" customWidth="1" style="54" min="4" max="4"/>
+    <col width="20" customWidth="1" style="54" min="5" max="5"/>
+    <col width="8" customWidth="1" style="54" min="6" max="7"/>
+    <col width="8.42578125" customWidth="1" style="54" min="8" max="8"/>
+    <col width="13" customWidth="1" style="54" min="9" max="9"/>
+    <col width="19" customWidth="1" style="54" min="10" max="10"/>
+    <col width="18" customWidth="1" style="54" min="11" max="11"/>
+    <col width="7" customWidth="1" style="54" min="12" max="12"/>
+    <col width="23" customWidth="1" style="54" min="13" max="13"/>
+    <col width="9" customWidth="1" style="54" min="14" max="14"/>
+    <col width="7" customWidth="1" style="54" min="15" max="15"/>
+    <col width="17" customWidth="1" style="54" min="16" max="16"/>
+    <col width="13" customWidth="1" style="54" min="17" max="17"/>
+    <col width="17" customWidth="1" style="54" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="52">
+    <row r="1" ht="25.5" customHeight="1" s="54">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>MOVES  -  the daily log</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="52">
+    <row r="2" ht="15" customHeight="1" s="54">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Pick the Movement first. The next column tells you exactly which fields to fill. Leave everything else blank.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="52">
+    <row r="4" ht="15" customHeight="1" s="54">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Made a mistake? Set Void to Yes. The row is ignored everywhere and stays visible. Never delete a row.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="31.5" customHeight="1" s="52">
+    <row r="6" ht="31.5" customHeight="1" s="54">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Date</t>
@@ -3857,7 +3932,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="52">
+    <row r="7" ht="15" customHeight="1" s="54">
       <c r="A7" s="34" t="n">
         <v>46258</v>
       </c>
@@ -3916,7 +3991,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="52">
+    <row r="8" ht="15" customHeight="1" s="54">
       <c r="A8" s="34" t="n">
         <v>46258</v>
       </c>
@@ -3975,7 +4050,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="52">
+    <row r="9" ht="15" customHeight="1" s="54">
       <c r="A9" s="34" t="n">
         <v>46258</v>
       </c>
@@ -4034,7 +4109,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="52">
+    <row r="10" ht="15" customHeight="1" s="54">
       <c r="A10" s="34" t="n">
         <v>46258</v>
       </c>
@@ -4093,7 +4168,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="52">
+    <row r="11" ht="15" customHeight="1" s="54">
       <c r="A11" s="34" t="n">
         <v>46258</v>
       </c>
@@ -4152,7 +4227,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="52">
+    <row r="12" ht="15" customHeight="1" s="54">
       <c r="A12" s="34" t="n">
         <v>46258</v>
       </c>
@@ -4211,7 +4286,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="52">
+    <row r="13" ht="15" customHeight="1" s="54">
       <c r="A13" s="34" t="n">
         <v>46258</v>
       </c>
@@ -4270,7 +4345,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="52">
+    <row r="14" ht="15" customHeight="1" s="54">
       <c r="A14" s="34" t="n">
         <v>46258</v>
       </c>
@@ -4329,7 +4404,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="52">
+    <row r="15" ht="15" customHeight="1" s="54">
       <c r="A15" s="34" t="n">
         <v>46258</v>
       </c>
@@ -4388,7 +4463,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="52">
+    <row r="16" ht="15" customHeight="1" s="54">
       <c r="A16" s="34" t="n">
         <v>46258</v>
       </c>
@@ -4447,7 +4522,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="52">
+    <row r="17" ht="15" customHeight="1" s="54">
       <c r="A17" s="34" t="n">
         <v>46258</v>
       </c>
@@ -4506,7 +4581,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="52">
+    <row r="18" ht="15" customHeight="1" s="54">
       <c r="A18" s="34" t="n">
         <v>46258</v>
       </c>
@@ -4565,7 +4640,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="52">
+    <row r="19" ht="15" customHeight="1" s="54">
       <c r="A19" s="34" t="n">
         <v>46258</v>
       </c>
@@ -4624,7 +4699,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="52">
+    <row r="20" ht="15" customHeight="1" s="54">
       <c r="A20" s="34" t="n">
         <v>46258</v>
       </c>
@@ -4683,7 +4758,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="52">
+    <row r="21" ht="15" customHeight="1" s="54">
       <c r="A21" s="34" t="n">
         <v>46258</v>
       </c>
@@ -4742,7 +4817,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="52">
+    <row r="22" ht="15" customHeight="1" s="54">
       <c r="A22" s="34" t="n">
         <v>46258</v>
       </c>
@@ -4801,7 +4876,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="52">
+    <row r="23" ht="15" customHeight="1" s="54">
       <c r="A23" s="34" t="n">
         <v>46258</v>
       </c>
@@ -4864,7 +4939,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="52">
+    <row r="24" ht="15" customHeight="1" s="54">
       <c r="A24" s="34" t="n">
         <v>46258</v>
       </c>
@@ -4927,7 +5002,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="52">
+    <row r="25" ht="15" customHeight="1" s="54">
       <c r="A25" s="34" t="n">
         <v>46258</v>
       </c>
@@ -4990,7 +5065,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="52">
+    <row r="26" ht="15" customHeight="1" s="54">
       <c r="A26" s="34" t="n">
         <v>46258</v>
       </c>
@@ -5053,7 +5128,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="52">
+    <row r="27" ht="15" customHeight="1" s="54">
       <c r="A27" s="34" t="n">
         <v>46258</v>
       </c>
@@ -5120,7 +5195,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="52">
+    <row r="28" ht="15" customHeight="1" s="54">
       <c r="A28" s="34" t="n">
         <v>46258</v>
       </c>
@@ -5184,7 +5259,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="57" t="n">
+      <c r="A29" s="49" t="n">
         <v>46260</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -5248,7 +5323,7 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="R29" s="58" t="n">
+      <c r="R29" s="50" t="n">
         <v>46260.9423210301</v>
       </c>
       <c r="S29" t="inlineStr">
@@ -5258,7 +5333,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="57" t="n">
+      <c r="A30" s="49" t="n">
         <v>46260</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -5322,7 +5397,7 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="R30" s="58" t="n">
+      <c r="R30" s="50" t="n">
         <v>46260.95209969908</v>
       </c>
       <c r="S30" t="inlineStr">
@@ -5332,7 +5407,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="57" t="n">
+      <c r="A31" s="49" t="n">
         <v>46260</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -5396,7 +5471,7 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="R31" s="58" t="n">
+      <c r="R31" s="50" t="n">
         <v>46260.96085467593</v>
       </c>
       <c r="S31" t="inlineStr">
@@ -5478,38 +5553,38 @@
   <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" style="52" min="1" max="1"/>
-    <col width="12" customWidth="1" style="52" min="2" max="2"/>
-    <col width="20" customWidth="1" style="52" min="3" max="3"/>
-    <col width="12" customWidth="1" style="52" min="4" max="4"/>
-    <col width="13" customWidth="1" style="52" min="5" max="5"/>
-    <col width="18" customWidth="1" style="52" min="6" max="6"/>
-    <col width="23" customWidth="1" style="52" min="7" max="7"/>
-    <col width="26" customWidth="1" style="52" min="8" max="8"/>
+    <col width="11" customWidth="1" style="54" min="1" max="1"/>
+    <col width="12" customWidth="1" style="54" min="2" max="2"/>
+    <col width="20" customWidth="1" style="54" min="3" max="3"/>
+    <col width="12" customWidth="1" style="54" min="4" max="4"/>
+    <col width="13" customWidth="1" style="54" min="5" max="5"/>
+    <col width="18" customWidth="1" style="54" min="6" max="6"/>
+    <col width="23" customWidth="1" style="54" min="7" max="7"/>
+    <col width="26" customWidth="1" style="54" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="52">
+    <row r="1" ht="25.5" customHeight="1" s="54">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>COUNT  -  physical stock check</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="52">
+    <row r="2" ht="15" customHeight="1" s="54">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Weekly or spot check. A count never changes stock - post a Count Adjustment in MOVES to correct it.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="52">
+    <row r="4" ht="15" customHeight="1" s="54">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Counted By is optional. Variance is calculated on the dashboard, not here.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="31.5" customHeight="1" s="52">
+    <row r="6" ht="31.5" customHeight="1" s="54">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Date</t>
@@ -5551,16 +5626,16 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="52"/>
-    <row r="8" ht="15" customHeight="1" s="52"/>
-    <row r="9" ht="15" customHeight="1" s="52"/>
-    <row r="10" ht="15" customHeight="1" s="52"/>
-    <row r="11" ht="15" customHeight="1" s="52"/>
-    <row r="12" ht="15" customHeight="1" s="52"/>
-    <row r="13" ht="15" customHeight="1" s="52"/>
-    <row r="14" ht="15" customHeight="1" s="52"/>
-    <row r="15" ht="15" customHeight="1" s="52"/>
-    <row r="16" ht="15" customHeight="1" s="52"/>
+    <row r="7" ht="15" customHeight="1" s="54"/>
+    <row r="8" ht="15" customHeight="1" s="54"/>
+    <row r="9" ht="15" customHeight="1" s="54"/>
+    <row r="10" ht="15" customHeight="1" s="54"/>
+    <row r="11" ht="15" customHeight="1" s="54"/>
+    <row r="12" ht="15" customHeight="1" s="54"/>
+    <row r="13" ht="15" customHeight="1" s="54"/>
+    <row r="14" ht="15" customHeight="1" s="54"/>
+    <row r="15" ht="15" customHeight="1" s="54"/>
+    <row r="16" ht="15" customHeight="1" s="54"/>
   </sheetData>
   <conditionalFormatting sqref="H7:H9000">
     <cfRule type="expression" priority="2" dxfId="0">
@@ -5595,38 +5670,38 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" style="52" min="1" max="1"/>
-    <col width="9" customWidth="1" style="52" min="2" max="2"/>
-    <col width="12" customWidth="1" style="52" min="3" max="4"/>
-    <col width="20" customWidth="1" style="52" min="5" max="5"/>
-    <col width="8" customWidth="1" style="52" min="6" max="6"/>
-    <col width="13" customWidth="1" style="52" min="7" max="7"/>
-    <col width="23" customWidth="1" style="52" min="8" max="8"/>
-    <col width="26" customWidth="1" style="52" min="9" max="9"/>
+    <col width="11" customWidth="1" style="54" min="1" max="1"/>
+    <col width="9" customWidth="1" style="54" min="2" max="2"/>
+    <col width="12" customWidth="1" style="54" min="3" max="4"/>
+    <col width="20" customWidth="1" style="54" min="5" max="5"/>
+    <col width="8" customWidth="1" style="54" min="6" max="6"/>
+    <col width="13" customWidth="1" style="54" min="7" max="7"/>
+    <col width="23" customWidth="1" style="54" min="8" max="8"/>
+    <col width="26" customWidth="1" style="54" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="52">
+    <row r="1" ht="25.5" customHeight="1" s="54">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>DISPATCH  -  written by the dashboard</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="52">
+    <row r="2" ht="15" customHeight="1" s="54">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>One row per order line dispatched. You do not type here - the Dispatch tab writes it when you confirm.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="52">
+    <row r="4" ht="15" customHeight="1" s="54">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>EXAMPLE row - delete it before you start.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="31.5" customHeight="1" s="52">
+    <row r="6" ht="31.5" customHeight="1" s="54">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Date</t>
@@ -5673,7 +5748,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="52">
+    <row r="7" ht="15" customHeight="1" s="54">
       <c r="A7" s="44" t="n"/>
       <c r="B7" s="45" t="n"/>
       <c r="C7" s="45" t="n"/>
@@ -5852,13 +5927,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DE7AC01-F156-4D0F-9089-DB8057DC708F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84D81202-C690-4C4F-88F9-3292E0CAE465}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65402AA4-0D3A-49D1-83D3-656FEE7755F3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47637D39-ED47-498C-A4AB-103DA6A3A42F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{176B3713-A76A-493A-8A45-CDF2C12E28DC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD51E8E6-1104-4166-8DBA-849C5D54171E}"/>
 </file>
--- a/Stock_Control/INRIPE_Stock_Entry_v1.xlsx
+++ b/Stock_Control/INRIPE_Stock_Entry_v1.xlsx
@@ -41,8 +41,8 @@
     <numFmt numFmtId="165" formatCode="dd\-mmm\-yy\ hh:mm"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
     <numFmt numFmtId="167" formatCode="dd\-mmm\-yy"/>
-    <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="169" formatCode="dd-mmm-yy"/>
+    <numFmt numFmtId="168" formatCode="dd-mmm-yy"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -362,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -492,6 +492,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1022,8 +1023,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tblShipment" displayName="tblShipment" ref="A6:I24" headerRowCount="1">
-  <autoFilter ref="A6:I24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tblShipment" displayName="tblShipment" ref="A6:I22" headerRowCount="1">
+  <autoFilter ref="A6:I22"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Shipment No"/>
     <tableColumn id="2" name="Market"/>
@@ -1035,7 +1036,7 @@
     <tableColumn id="8" name="Item Code"/>
     <tableColumn id="9" name="Check"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
 </file>
 
@@ -1602,7 +1603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB32"/>
+  <dimension ref="A1:AB31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" style="54" min="1" max="1"/>
@@ -2858,7 +2859,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -2880,7 +2880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="54" min="1" max="1"/>
@@ -2973,7 +2973,7 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="C7" s="48" t="n">
+      <c r="C7" s="58" t="n">
         <v>46258</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -3011,7 +3011,7 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="C8" s="48" t="n">
+      <c r="C8" s="58" t="n">
         <v>46258</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -3049,7 +3049,7 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="C9" s="48" t="n">
+      <c r="C9" s="58" t="n">
         <v>46258</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -3087,7 +3087,7 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="C10" s="48" t="n">
+      <c r="C10" s="58" t="n">
         <v>46258</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -3125,7 +3125,7 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="C11" s="48" t="n">
+      <c r="C11" s="58" t="n">
         <v>46258</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -3163,7 +3163,7 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="C12" s="48" t="n">
+      <c r="C12" s="58" t="n">
         <v>46258</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -3201,7 +3201,7 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="C13" s="48" t="n">
+      <c r="C13" s="58" t="n">
         <v>46258</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -3239,7 +3239,7 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="C14" s="48" t="n">
+      <c r="C14" s="58" t="n">
         <v>46258</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -3277,7 +3277,7 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="C15" s="48" t="n">
+      <c r="C15" s="58" t="n">
         <v>46258</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -3315,7 +3315,7 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="C16" s="48" t="n">
+      <c r="C16" s="58" t="n">
         <v>46258</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -3353,7 +3353,7 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="C17" s="48" t="n">
+      <c r="C17" s="58" t="n">
         <v>46258</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -3391,7 +3391,7 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="C18" s="48" t="n">
+      <c r="C18" s="58" t="n">
         <v>46258</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -3429,7 +3429,7 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="C19" s="48" t="n">
+      <c r="C19" s="58" t="n">
         <v>46258</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -3467,7 +3467,7 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="C20" s="48" t="n">
+      <c r="C20" s="58" t="n">
         <v>46258</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -3505,7 +3505,7 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="C21" s="48" t="n">
+      <c r="C21" s="58" t="n">
         <v>46258</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -3543,7 +3543,7 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="C22" s="48" t="n">
+      <c r="C22" s="58" t="n">
         <v>46258</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -3570,82 +3570,8 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="54">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Q-26-002</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C23" s="57" t="n">
-        <v>46261</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Grapes Banati</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>EG-FG-GRP-01-02-01-01</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="54">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Q-26-002</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C24" s="57" t="n">
-        <v>46261</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Fig Barshomi</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>EG-FG-FIG-01-02-01-01</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
+    <row r="23" ht="15" customHeight="1" s="54"/>
+    <row r="24" ht="15" customHeight="1" s="54"/>
     <row r="25" ht="15" customHeight="1" s="54"/>
     <row r="26" ht="15" customHeight="1" s="54"/>
     <row r="27" ht="15" customHeight="1" s="54"/>
@@ -5927,13 +5853,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84D81202-C690-4C4F-88F9-3292E0CAE465}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E62F00BC-2969-4C87-BF1B-143542CAAA8B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47637D39-ED47-498C-A4AB-103DA6A3A42F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{433234C5-CD61-4E2C-BE36-BF3250E08EAC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD51E8E6-1104-4166-8DBA-849C5D54171E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EBBA444-FA7E-4F1E-8420-D2094FE9A024}"/>
 </file>
--- a/Stock_Control/INRIPE_Stock_Entry_v1.xlsx
+++ b/Stock_Control/INRIPE_Stock_Entry_v1.xlsx
@@ -1055,8 +1055,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tblMoves" displayName="tblMoves" ref="A6:S46" headerRowCount="1">
-  <autoFilter ref="A6:S46"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tblMoves" displayName="tblMoves" ref="A6:S48" headerRowCount="1">
+  <autoFilter ref="A6:S48"/>
   <tableColumns count="19">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Shipment No"/>
@@ -4226,7 +4226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S46"/>
+  <dimension ref="A1:S48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="55" min="1" max="1"/>
@@ -6889,6 +6889,149 @@
         <v>46263.73066756944</v>
       </c>
       <c r="S46" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="59" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Q-26-003</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Scrap</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>OUT   fill: Item  Out  Reason</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Mango Owais</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>EG-FG-MNG-12-02-01-01</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>2</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Q-20260829-0009</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="R47" s="61" t="n">
+        <v>46263.77142931713</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="59" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Q-26-003</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Returned</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>IN   fill: Item  In  Courier  Reason</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Mango Owais</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>6</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>WareOne</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Customer Refused</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>voided by admin 29 Aug 18:36</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>EG-FG-MNG-12-02-01-01</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>6</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Q-20260829-0010</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="R48" s="61" t="n">
+        <v>46263.7751134838</v>
+      </c>
+      <c r="S48" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7341,13 +7484,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E563BDE5-E042-4CA8-AC57-F2D89BB94699}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{659E6CF3-0F4A-409D-AD14-4AE7D4F368A4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0808022B-9704-4150-8BFC-D3B6C7A25640}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E868B1FC-FDA7-4769-B050-5BF2503A6552}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDF720B3-3595-49CC-902E-636FB545B866}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00243A3-8AF8-403A-8C03-4281C387CE91}"/>
 </file>
--- a/Stock_Control/INRIPE_Stock_Entry_v1.xlsx
+++ b/Stock_Control/INRIPE_Stock_Entry_v1.xlsx
@@ -44,7 +44,7 @@
     <numFmt numFmtId="168" formatCode="dd-mmm-yy"/>
     <numFmt numFmtId="169" formatCode="dd-mmm-yy hh:mm"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -218,8 +218,14 @@
       <name val="Arial"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -297,8 +303,13 @@
         <fgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00152947"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -367,11 +378,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -508,6 +533,12 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -955,7 +986,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="tblDispatch" displayName="tblDispatch" ref="A6:I7" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="tblDispatch" displayName="tblDispatch" ref="A6:I7" headerRowCount="1">
   <autoFilter ref="A6:I7"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Date"/>
@@ -968,7 +999,7 @@
     <tableColumn id="8" name="Item Code"/>
     <tableColumn id="9" name="Check"/>
   </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
 </file>
 
@@ -1037,26 +1068,27 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tblShipment" displayName="tblShipment" ref="A6:I28" headerRowCount="1">
-  <autoFilter ref="A6:I28"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tblShipment" displayName="tblShipment" ref="A6:J7" headerRowCount="1">
+  <autoFilter ref="A6:J7"/>
+  <tableColumns count="10">
     <tableColumn id="1" name="Shipment No"/>
     <tableColumn id="2" name="Market"/>
     <tableColumn id="3" name="Arrival Date"/>
     <tableColumn id="4" name="Source"/>
     <tableColumn id="5" name="Item Name"/>
     <tableColumn id="6" name="Shipped Qty"/>
-    <tableColumn id="7" name="Note"/>
-    <tableColumn id="8" name="Item Code"/>
-    <tableColumn id="9" name="Check"/>
+    <tableColumn id="7" name="PO Qty"/>
+    <tableColumn id="8" name="Note"/>
+    <tableColumn id="9" name="Item Code"/>
+    <tableColumn id="10" name="Check"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tblMoves" displayName="tblMoves" ref="A6:S48" headerRowCount="1">
-  <autoFilter ref="A6:S48"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tblMoves" displayName="tblMoves" ref="A6:S7" headerRowCount="1">
+  <autoFilter ref="A6:S7"/>
   <tableColumns count="19">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Shipment No"/>
@@ -1078,7 +1110,7 @@
     <tableColumn id="18" name="Entered at"/>
     <tableColumn id="19" name="Check"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
 </file>
 
@@ -1095,7 +1127,7 @@
     <tableColumn id="7" name="Item Code"/>
     <tableColumn id="8" name="Check"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
 </file>
 
@@ -3166,7 +3198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="55" min="1" max="1"/>
@@ -3232,858 +3264,49 @@
           <t>Shipped Qty</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="62" t="inlineStr">
+        <is>
+          <t>PO Qty</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="H6" s="37" t="inlineStr">
+      <c r="I6" s="37" t="inlineStr">
         <is>
           <t>Item Code</t>
         </is>
       </c>
-      <c r="I6" s="37" t="inlineStr">
+      <c r="J6" s="37" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="55">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="n">
-        <v>46258</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Cantaloupe</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>15</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>EG-FG-CAN-01-02-01-01</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="55">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="n">
-        <v>46258</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Dates Barhi</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>EG-FG-DAT-01-02-01-01</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="55">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="n">
-        <v>46258</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Fig Barshomi</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>40</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>EG-FG-FIG-01-02-01-01</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="55">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="n">
-        <v>46258</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Grapes Banati</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>18</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>EG-FG-GRP-01-02-01-01</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="55">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="n">
-        <v>46258</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Grapes Red</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>13</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>EG-FG-GRP-03-02-01-01</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="55">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>46258</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Guava Banati</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>38</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>EG-FG-GUV-01-02-01-01</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="55">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>46258</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Mango Fas</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>98</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-05-02-01-01</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="55">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>46258</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Mango Fons</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>18</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-06-02-01-01</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="55">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>46258</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Mango Naomi</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>15</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-11-02-01-01</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="55">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="n">
-        <v>46258</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Mango Owais</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>43</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-12-02-01-01</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="55">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="n">
-        <v>46258</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Mango Sediqa</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-15-02-01-01</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="55">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="n">
-        <v>46258</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Mango Timour</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>4</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-17-02-01-01</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="55">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="n">
-        <v>46258</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Mango White Sugar</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-18-02-01-01</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="55">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="n">
-        <v>46258</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Mango Trio Box</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>55</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-20-02-01-01</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="55">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="n">
-        <v>46258</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Mango Zebda</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>8</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-19-02-01-01</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="55">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="n">
-        <v>46258</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Pear Banati</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>10</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>EG-FG-PER-01-02-01-01</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="55">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Q-26-002</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="n">
-        <v>46262</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Mango Fas</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>50</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-05-02-01-01</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="55">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Q-26-002</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="n">
-        <v>46262</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Mango Owais</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>30</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-12-02-01-01</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="55">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Q-26-002</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="n">
-        <v>46262</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Fig Barshomi</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>20</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>EG-FG-FIG-01-02-01-01</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="55">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Q-26-003</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C26" s="59" t="n">
-        <v>46263</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Mango Fas</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>50</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-05-02-01-01</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="55">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Q-26-003</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C27" s="59" t="n">
-        <v>46263</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Mango Owais</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>30</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-12-02-01-01</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="55">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Q-26-003</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C28" s="59" t="n">
-        <v>46263</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Fig Barshomi</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>20</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>EG-FG-FIG-01-02-01-01</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
+    <row r="7" ht="15" customHeight="1" s="55"/>
+    <row r="8" ht="15" customHeight="1" s="55"/>
+    <row r="9" ht="15" customHeight="1" s="55"/>
+    <row r="10" ht="15" customHeight="1" s="55"/>
+    <row r="11" ht="15" customHeight="1" s="55"/>
+    <row r="12" ht="15" customHeight="1" s="55"/>
+    <row r="13" ht="15" customHeight="1" s="55"/>
+    <row r="14" ht="15" customHeight="1" s="55"/>
+    <row r="15" ht="15" customHeight="1" s="55"/>
+    <row r="16" ht="15" customHeight="1" s="55"/>
+    <row r="17" ht="15" customHeight="1" s="55"/>
+    <row r="18" ht="15" customHeight="1" s="55"/>
+    <row r="19" ht="15" customHeight="1" s="55"/>
+    <row r="20" ht="15" customHeight="1" s="55"/>
+    <row r="21" ht="15" customHeight="1" s="55"/>
+    <row r="22" ht="15" customHeight="1" s="55"/>
+    <row r="23" ht="15" customHeight="1" s="55"/>
+    <row r="24" ht="15" customHeight="1" s="55"/>
+    <row r="25" ht="15" customHeight="1" s="55"/>
+    <row r="26" ht="15" customHeight="1" s="55"/>
+    <row r="27" ht="15" customHeight="1" s="55"/>
+    <row r="28" ht="15" customHeight="1" s="55"/>
     <row r="29" ht="15" customHeight="1" s="55"/>
     <row r="30" ht="15" customHeight="1" s="55"/>
     <row r="31" ht="15" customHeight="1" s="55"/>
@@ -4226,7 +3449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S48"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="55" min="1" max="1"/>
@@ -4366,2677 +3589,28 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="55">
-      <c r="A7" s="39" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B7" s="40" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C7" s="40" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="D7" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IN   fill: Item  In  </t>
-        </is>
-      </c>
-      <c r="E7" s="42" t="inlineStr">
-        <is>
-          <t>Cantaloupe</t>
-        </is>
-      </c>
-      <c r="F7" s="43" t="n">
-        <v>15</v>
-      </c>
-      <c r="G7" s="44" t="n"/>
-      <c r="H7" s="44" t="n"/>
-      <c r="I7" s="40" t="n"/>
-      <c r="J7" s="40" t="n"/>
-      <c r="K7" s="40" t="n"/>
-      <c r="L7" s="40" t="n"/>
-      <c r="M7" s="41" t="inlineStr">
-        <is>
-          <t>EG-FG-CAN-01-02-01-01</t>
-        </is>
-      </c>
-      <c r="N7" s="41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O7" s="45" t="n">
-        <v>15</v>
-      </c>
-      <c r="P7" s="46" t="n"/>
-      <c r="Q7" s="46" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="R7" s="47" t="n"/>
-      <c r="S7" s="41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="55">
-      <c r="A8" s="39" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B8" s="40" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C8" s="40" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="D8" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IN   fill: Item  In  </t>
-        </is>
-      </c>
-      <c r="E8" s="48" t="inlineStr">
-        <is>
-          <t>Dates Barhi</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" s="44" t="n"/>
-      <c r="H8" s="44" t="n"/>
-      <c r="I8" s="40" t="n"/>
-      <c r="J8" s="40" t="n"/>
-      <c r="K8" s="40" t="n"/>
-      <c r="L8" s="40" t="n"/>
-      <c r="M8" s="41" t="inlineStr">
-        <is>
-          <t>EG-FG-DAT-01-02-01-01</t>
-        </is>
-      </c>
-      <c r="N8" s="41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O8" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="P8" s="46" t="n"/>
-      <c r="Q8" s="46" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="R8" s="47" t="n"/>
-      <c r="S8" s="41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="55">
-      <c r="A9" s="39" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B9" s="40" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C9" s="40" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="D9" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IN   fill: Item  In  </t>
-        </is>
-      </c>
-      <c r="E9" s="48" t="inlineStr">
-        <is>
-          <t>Fig Barshomi</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="G9" s="44" t="n"/>
-      <c r="H9" s="44" t="n"/>
-      <c r="I9" s="40" t="n"/>
-      <c r="J9" s="40" t="n"/>
-      <c r="K9" s="40" t="n"/>
-      <c r="L9" s="40" t="n"/>
-      <c r="M9" s="41" t="inlineStr">
-        <is>
-          <t>EG-FG-FIG-01-02-01-01</t>
-        </is>
-      </c>
-      <c r="N9" s="41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O9" s="45" t="n">
-        <v>40</v>
-      </c>
-      <c r="P9" s="46" t="n"/>
-      <c r="Q9" s="46" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="R9" s="47" t="n"/>
-      <c r="S9" s="41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="55">
-      <c r="A10" s="39" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B10" s="40" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C10" s="40" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="D10" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IN   fill: Item  In  </t>
-        </is>
-      </c>
-      <c r="E10" s="48" t="inlineStr">
-        <is>
-          <t>Grapes Banati</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="G10" s="44" t="n"/>
-      <c r="H10" s="44" t="n"/>
-      <c r="I10" s="40" t="n"/>
-      <c r="J10" s="40" t="n"/>
-      <c r="K10" s="40" t="n"/>
-      <c r="L10" s="40" t="n"/>
-      <c r="M10" s="41" t="inlineStr">
-        <is>
-          <t>EG-FG-GRP-01-02-01-01</t>
-        </is>
-      </c>
-      <c r="N10" s="41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O10" s="45" t="n">
-        <v>18</v>
-      </c>
-      <c r="P10" s="46" t="n"/>
-      <c r="Q10" s="46" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="R10" s="47" t="n"/>
-      <c r="S10" s="41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="55">
-      <c r="A11" s="39" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B11" s="40" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C11" s="40" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="D11" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IN   fill: Item  In  </t>
-        </is>
-      </c>
-      <c r="E11" s="48" t="inlineStr">
-        <is>
-          <t>Grapes Red</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="G11" s="44" t="n"/>
-      <c r="H11" s="44" t="n"/>
-      <c r="I11" s="40" t="n"/>
-      <c r="J11" s="40" t="n"/>
-      <c r="K11" s="40" t="n"/>
-      <c r="L11" s="40" t="n"/>
-      <c r="M11" s="41" t="inlineStr">
-        <is>
-          <t>EG-FG-GRP-03-02-01-01</t>
-        </is>
-      </c>
-      <c r="N11" s="41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O11" s="45" t="n">
-        <v>13</v>
-      </c>
-      <c r="P11" s="46" t="n"/>
-      <c r="Q11" s="46" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="R11" s="47" t="n"/>
-      <c r="S11" s="41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="55">
-      <c r="A12" s="39" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B12" s="40" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C12" s="40" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="D12" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IN   fill: Item  In  </t>
-        </is>
-      </c>
-      <c r="E12" s="48" t="inlineStr">
-        <is>
-          <t>Guava Banati</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="G12" s="44" t="n"/>
-      <c r="H12" s="44" t="n"/>
-      <c r="I12" s="40" t="n"/>
-      <c r="J12" s="40" t="n"/>
-      <c r="K12" s="40" t="n"/>
-      <c r="L12" s="40" t="n"/>
-      <c r="M12" s="41" t="inlineStr">
-        <is>
-          <t>EG-FG-GUV-01-02-01-01</t>
-        </is>
-      </c>
-      <c r="N12" s="41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O12" s="45" t="n">
-        <v>38</v>
-      </c>
-      <c r="P12" s="46" t="n"/>
-      <c r="Q12" s="46" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="R12" s="47" t="n"/>
-      <c r="S12" s="41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="55">
-      <c r="A13" s="39" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B13" s="40" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C13" s="40" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="D13" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IN   fill: Item  In  </t>
-        </is>
-      </c>
-      <c r="E13" s="48" t="inlineStr">
-        <is>
-          <t>Mango Fas</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>98</v>
-      </c>
-      <c r="G13" s="44" t="n"/>
-      <c r="H13" s="44" t="n"/>
-      <c r="I13" s="40" t="n"/>
-      <c r="J13" s="40" t="n"/>
-      <c r="K13" s="40" t="n"/>
-      <c r="L13" s="40" t="n"/>
-      <c r="M13" s="41" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-05-02-01-01</t>
-        </is>
-      </c>
-      <c r="N13" s="41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O13" s="45" t="n">
-        <v>98</v>
-      </c>
-      <c r="P13" s="46" t="n"/>
-      <c r="Q13" s="46" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="R13" s="47" t="n"/>
-      <c r="S13" s="41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="55">
-      <c r="A14" s="39" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B14" s="40" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C14" s="40" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="D14" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IN   fill: Item  In  </t>
-        </is>
-      </c>
-      <c r="E14" s="48" t="inlineStr">
-        <is>
-          <t>Mango Fons</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="G14" s="44" t="n"/>
-      <c r="H14" s="44" t="n"/>
-      <c r="I14" s="40" t="n"/>
-      <c r="J14" s="40" t="n"/>
-      <c r="K14" s="40" t="n"/>
-      <c r="L14" s="40" t="n"/>
-      <c r="M14" s="41" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-06-02-01-01</t>
-        </is>
-      </c>
-      <c r="N14" s="41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O14" s="45" t="n">
-        <v>18</v>
-      </c>
-      <c r="P14" s="46" t="n"/>
-      <c r="Q14" s="46" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="R14" s="47" t="n"/>
-      <c r="S14" s="41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="55">
-      <c r="A15" s="39" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B15" s="40" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C15" s="40" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="D15" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IN   fill: Item  In  </t>
-        </is>
-      </c>
-      <c r="E15" s="48" t="inlineStr">
-        <is>
-          <t>Mango Naomi</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="G15" s="44" t="n"/>
-      <c r="H15" s="44" t="n"/>
-      <c r="I15" s="40" t="n"/>
-      <c r="J15" s="40" t="n"/>
-      <c r="K15" s="40" t="n"/>
-      <c r="L15" s="40" t="n"/>
-      <c r="M15" s="41" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-11-02-01-01</t>
-        </is>
-      </c>
-      <c r="N15" s="41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O15" s="45" t="n">
-        <v>15</v>
-      </c>
-      <c r="P15" s="46" t="n"/>
-      <c r="Q15" s="46" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="R15" s="47" t="n"/>
-      <c r="S15" s="41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="55">
-      <c r="A16" s="39" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B16" s="40" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C16" s="40" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="D16" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IN   fill: Item  In  </t>
-        </is>
-      </c>
-      <c r="E16" s="48" t="inlineStr">
-        <is>
-          <t>Mango Owais</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>43</v>
-      </c>
-      <c r="G16" s="44" t="n"/>
-      <c r="H16" s="44" t="n"/>
-      <c r="I16" s="40" t="n"/>
-      <c r="J16" s="40" t="n"/>
-      <c r="K16" s="40" t="n"/>
-      <c r="L16" s="40" t="n"/>
-      <c r="M16" s="41" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-12-02-01-01</t>
-        </is>
-      </c>
-      <c r="N16" s="41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O16" s="45" t="n">
-        <v>43</v>
-      </c>
-      <c r="P16" s="46" t="n"/>
-      <c r="Q16" s="46" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="R16" s="47" t="n"/>
-      <c r="S16" s="41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="55">
-      <c r="A17" s="39" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B17" s="40" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C17" s="40" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="D17" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IN   fill: Item  In  </t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>Mango Sediqa</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" s="44" t="n"/>
-      <c r="H17" s="44" t="n"/>
-      <c r="I17" s="40" t="n"/>
-      <c r="J17" s="40" t="n"/>
-      <c r="K17" s="40" t="n"/>
-      <c r="L17" s="40" t="n"/>
-      <c r="M17" s="41" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-15-02-01-01</t>
-        </is>
-      </c>
-      <c r="N17" s="41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O17" s="45" t="n">
-        <v>3</v>
-      </c>
-      <c r="P17" s="46" t="n"/>
-      <c r="Q17" s="46" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="R17" s="47" t="n"/>
-      <c r="S17" s="41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="55">
-      <c r="A18" s="39" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B18" s="40" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C18" s="40" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="D18" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IN   fill: Item  In  </t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>Mango Timour</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="G18" s="44" t="n"/>
-      <c r="H18" s="44" t="n"/>
-      <c r="I18" s="40" t="n"/>
-      <c r="J18" s="40" t="n"/>
-      <c r="K18" s="40" t="n"/>
-      <c r="L18" s="40" t="n"/>
-      <c r="M18" s="41" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-17-02-01-01</t>
-        </is>
-      </c>
-      <c r="N18" s="41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O18" s="45" t="n">
-        <v>3</v>
-      </c>
-      <c r="P18" s="46" t="n"/>
-      <c r="Q18" s="46" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="R18" s="47" t="n"/>
-      <c r="S18" s="41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="55">
-      <c r="A19" s="39" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B19" s="40" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C19" s="40" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="D19" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IN   fill: Item  In  </t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>Mango White Sugar</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" s="44" t="n"/>
-      <c r="H19" s="44" t="n"/>
-      <c r="I19" s="40" t="n"/>
-      <c r="J19" s="40" t="n"/>
-      <c r="K19" s="40" t="n"/>
-      <c r="L19" s="40" t="n"/>
-      <c r="M19" s="41" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-18-02-01-01</t>
-        </is>
-      </c>
-      <c r="N19" s="41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O19" s="45" t="n">
-        <v>10</v>
-      </c>
-      <c r="P19" s="46" t="n"/>
-      <c r="Q19" s="46" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="R19" s="47" t="n"/>
-      <c r="S19" s="41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="55">
-      <c r="A20" s="39" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B20" s="40" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C20" s="40" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="D20" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IN   fill: Item  In  </t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>Mango Trio Box</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="G20" s="44" t="n"/>
-      <c r="H20" s="44" t="n"/>
-      <c r="I20" s="40" t="n"/>
-      <c r="J20" s="40" t="n"/>
-      <c r="K20" s="40" t="n"/>
-      <c r="L20" s="40" t="n"/>
-      <c r="M20" s="41" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-20-02-01-01</t>
-        </is>
-      </c>
-      <c r="N20" s="41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O20" s="45" t="n">
-        <v>55</v>
-      </c>
-      <c r="P20" s="46" t="n"/>
-      <c r="Q20" s="46" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="R20" s="47" t="n"/>
-      <c r="S20" s="41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="55">
-      <c r="A21" s="39" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B21" s="40" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C21" s="40" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="D21" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IN   fill: Item  In  </t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>Mango Zebda</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="G21" s="44" t="n"/>
-      <c r="H21" s="44" t="n"/>
-      <c r="I21" s="40" t="n"/>
-      <c r="J21" s="40" t="n"/>
-      <c r="K21" s="40" t="n"/>
-      <c r="L21" s="40" t="n"/>
-      <c r="M21" s="41" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-19-02-01-01</t>
-        </is>
-      </c>
-      <c r="N21" s="41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O21" s="45" t="n">
-        <v>8</v>
-      </c>
-      <c r="P21" s="46" t="n"/>
-      <c r="Q21" s="46" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="R21" s="47" t="n"/>
-      <c r="S21" s="41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="55">
-      <c r="A22" s="39" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B22" s="40" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C22" s="40" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="D22" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IN   fill: Item  In  </t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>Pear Banati</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="G22" s="44" t="n"/>
-      <c r="H22" s="44" t="n"/>
-      <c r="I22" s="40" t="n"/>
-      <c r="J22" s="40" t="n"/>
-      <c r="K22" s="40" t="n"/>
-      <c r="L22" s="40" t="n"/>
-      <c r="M22" s="41" t="inlineStr">
-        <is>
-          <t>EG-FG-PER-01-02-01-01</t>
-        </is>
-      </c>
-      <c r="N22" s="41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O22" s="45" t="n">
-        <v>10</v>
-      </c>
-      <c r="P22" s="46" t="n"/>
-      <c r="Q22" s="46" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="R22" s="47" t="n"/>
-      <c r="S22" s="41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="55">
-      <c r="A23" s="39" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B23" s="40" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C23" s="40" t="inlineStr">
-        <is>
-          <t>Scrap</t>
-        </is>
-      </c>
-      <c r="D23" s="41" t="inlineStr">
-        <is>
-          <t>OUT   fill: Item  Out  Reason</t>
-        </is>
-      </c>
-      <c r="E23" s="48" t="inlineStr">
-        <is>
-          <t>Fig Barshomi</t>
-        </is>
-      </c>
-      <c r="F23" s="43" t="n"/>
-      <c r="G23" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" s="44" t="n"/>
-      <c r="I23" s="40" t="n"/>
-      <c r="J23" s="40" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="K23" s="40" t="n"/>
-      <c r="L23" s="40" t="n"/>
-      <c r="M23" s="41" t="inlineStr">
-        <is>
-          <t>EG-FG-FIG-01-02-01-01</t>
-        </is>
-      </c>
-      <c r="N23" s="41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O23" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="P23" s="46" t="n"/>
-      <c r="Q23" s="46" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="R23" s="47" t="n"/>
-      <c r="S23" s="41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="55">
-      <c r="A24" s="39" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B24" s="40" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C24" s="40" t="inlineStr">
-        <is>
-          <t>Scrap</t>
-        </is>
-      </c>
-      <c r="D24" s="41" t="inlineStr">
-        <is>
-          <t>OUT   fill: Item  Out  Reason</t>
-        </is>
-      </c>
-      <c r="E24" s="48" t="inlineStr">
-        <is>
-          <t>Guava Banati</t>
-        </is>
-      </c>
-      <c r="F24" s="43" t="n"/>
-      <c r="G24" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="44" t="n"/>
-      <c r="I24" s="40" t="n"/>
-      <c r="J24" s="40" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="K24" s="40" t="n"/>
-      <c r="L24" s="40" t="n"/>
-      <c r="M24" s="41" t="inlineStr">
-        <is>
-          <t>EG-FG-GUV-01-02-01-01</t>
-        </is>
-      </c>
-      <c r="N24" s="41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O24" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="P24" s="46" t="n"/>
-      <c r="Q24" s="46" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="R24" s="47" t="n"/>
-      <c r="S24" s="41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="55">
-      <c r="A25" s="39" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B25" s="40" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C25" s="40" t="inlineStr">
-        <is>
-          <t>Scrap</t>
-        </is>
-      </c>
-      <c r="D25" s="41" t="inlineStr">
-        <is>
-          <t>OUT   fill: Item  Out  Reason</t>
-        </is>
-      </c>
-      <c r="E25" s="48" t="inlineStr">
-        <is>
-          <t>Mango Fas</t>
-        </is>
-      </c>
-      <c r="F25" s="43" t="n"/>
-      <c r="G25" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="44" t="n"/>
-      <c r="I25" s="40" t="n"/>
-      <c r="J25" s="40" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="K25" s="40" t="n"/>
-      <c r="L25" s="40" t="n"/>
-      <c r="M25" s="41" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-05-02-01-01</t>
-        </is>
-      </c>
-      <c r="N25" s="41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O25" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="P25" s="46" t="n"/>
-      <c r="Q25" s="46" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="R25" s="47" t="n"/>
-      <c r="S25" s="41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="55">
-      <c r="A26" s="39" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B26" s="40" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C26" s="40" t="inlineStr">
-        <is>
-          <t>Scrap</t>
-        </is>
-      </c>
-      <c r="D26" s="41" t="inlineStr">
-        <is>
-          <t>OUT   fill: Item  Out  Reason</t>
-        </is>
-      </c>
-      <c r="E26" s="48" t="inlineStr">
-        <is>
-          <t>Mango Owais</t>
-        </is>
-      </c>
-      <c r="F26" s="43" t="n"/>
-      <c r="G26" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="44" t="n"/>
-      <c r="I26" s="40" t="n"/>
-      <c r="J26" s="40" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="K26" s="40" t="n"/>
-      <c r="L26" s="40" t="n"/>
-      <c r="M26" s="41" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-12-02-01-01</t>
-        </is>
-      </c>
-      <c r="N26" s="41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O26" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="P26" s="46" t="n"/>
-      <c r="Q26" s="46" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="R26" s="47" t="n"/>
-      <c r="S26" s="41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="55">
-      <c r="A27" s="39" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B27" s="40" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C27" s="40" t="inlineStr">
-        <is>
-          <t>Not received</t>
-        </is>
-      </c>
-      <c r="D27" s="41" t="inlineStr">
-        <is>
-          <t>OUT   fill: Item  Out  Reason</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>Mango Timour</t>
-        </is>
-      </c>
-      <c r="F27" s="43" t="n"/>
-      <c r="G27" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="44" t="n"/>
-      <c r="I27" s="40" t="n"/>
-      <c r="J27" s="40" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="K27" s="40" t="inlineStr">
-        <is>
-          <t>Certification</t>
-        </is>
-      </c>
-      <c r="L27" s="40" t="n"/>
-      <c r="M27" s="41" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-17-02-01-01</t>
-        </is>
-      </c>
-      <c r="N27" s="41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O27" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" s="46" t="n"/>
-      <c r="Q27" s="46" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="R27" s="47" t="n"/>
-      <c r="S27" s="41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="55">
-      <c r="A28" s="39" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B28" s="40" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C28" s="40" t="inlineStr">
-        <is>
-          <t>Scrap</t>
-        </is>
-      </c>
-      <c r="D28" s="41" t="inlineStr">
-        <is>
-          <t>OUT   fill: Item  Out  Reason</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>Mango White Sugar</t>
-        </is>
-      </c>
-      <c r="F28" s="43" t="n"/>
-      <c r="G28" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="44" t="n"/>
-      <c r="I28" s="40" t="n"/>
-      <c r="J28" s="40" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="K28" s="40" t="n"/>
-      <c r="L28" s="40" t="n"/>
-      <c r="M28" s="41" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-18-02-01-01</t>
-        </is>
-      </c>
-      <c r="N28" s="41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O28" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="P28" s="46" t="n"/>
-      <c r="Q28" s="46" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="R28" s="47" t="n"/>
-      <c r="S28" s="41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="13" t="n">
-        <v>46260</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Not received</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>OUT   fill: Item  Out  Reason</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Mango Timour</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Customs</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>voided by admin 26 Aug 22:42</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-17-02-01-01</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O29" t="n">
-        <v>1</v>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Q-20260826-0001</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="R29" s="14" t="n">
-        <v>46260.9423210301</v>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="13" t="n">
-        <v>46260</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Not received</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>OUT   fill: Item  Out  Reason</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Mango Timour</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Customs</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>voided: more was recorded as not received than was ever shipped</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-17-02-01-01</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O30" t="n">
-        <v>1</v>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Q-20260826-0002</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="R30" s="14" t="n">
-        <v>46260.95209969908</v>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="13" t="n">
-        <v>46260</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Q-26-001</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Not received</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>OUT   fill: Item  Out  Reason</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Mango Timour</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Customs</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>voided by admin 26 Aug 23:31</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-17-02-01-01</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O31" t="n">
-        <v>1</v>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Q-20260826-0003</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="R31" s="14" t="n">
-        <v>46260.96085467593</v>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="13" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Q-26-002</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IN   fill: Item  In  </t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Fig Barshomi</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>20</v>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>EG-FG-FIG-01-02-01-01</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O32" t="n">
-        <v>20</v>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Q-20260828-0001</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="R32" s="14" t="n">
-        <v>46262.88776798611</v>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="13" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Q-26-002</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IN   fill: Item  In  </t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Mango Fas</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>47</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-05-02-01-01</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O33" t="n">
-        <v>47</v>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Q-20260828-0002</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="R33" s="14" t="n">
-        <v>46262.88776798611</v>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="13" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Q-26-002</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IN   fill: Item  In  </t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Mango Owais</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>30</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-12-02-01-01</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O34" t="n">
-        <v>30</v>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Q-20260828-0003</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="R34" s="14" t="n">
-        <v>46262.88776798611</v>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="13" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Q-26-002</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Not received</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>OUT   fill: Item  Out  Reason</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Mango Fas</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>3</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Customs</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-05-02-01-01</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O35" t="n">
-        <v>3</v>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Q-20260828-0004</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="R35" s="14" t="n">
-        <v>46262.89078278935</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="13" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Q-26-002</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Scrap</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>OUT   fill: Item  Out  Reason</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Mango Owais</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-12-02-01-01</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O36" t="n">
-        <v>2</v>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Q-20260828-0005</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="R36" s="14" t="n">
-        <v>46262.89313989583</v>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="13" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Q-26-002</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>To Courier</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OUT   fill: Item  Out  Courier  </t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Mango Owais</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>28</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>WareOne</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-12-02-01-01</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O37" t="n">
-        <v>28</v>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Q-20260828-0006</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="R37" s="14" t="n">
-        <v>46262.89378311342</v>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="13" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Q-26-002</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Returned</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>IN   fill: Item  In  Courier  Reason</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Mango Owais</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>6</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>WareOne</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Customer Refused</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>voided by admin 28 Aug 21:30</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-12-02-01-01</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O38" t="n">
-        <v>6</v>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Q-20260828-0007</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="R38" s="14" t="n">
-        <v>46262.89572866898</v>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="59" t="n">
-        <v>46263</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Q-26-003</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IN   fill: Item  In  </t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Fig Barshomi</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>20</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>EG-FG-FIG-01-02-01-01</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O39" t="n">
-        <v>20</v>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Q-20260829-0001</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="R39" s="61" t="n">
-        <v>46263.7222853588</v>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="59" t="n">
-        <v>46263</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Q-26-003</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IN   fill: Item  In  </t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Mango Fas</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>47</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-05-02-01-01</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O40" t="n">
-        <v>47</v>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Q-20260829-0002</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="R40" s="61" t="n">
-        <v>46263.7222853588</v>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="59" t="n">
-        <v>46263</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Q-26-003</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IN   fill: Item  In  </t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Mango Owais</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>30</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-12-02-01-01</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O41" t="n">
-        <v>30</v>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Q-20260829-0003</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="R41" s="61" t="n">
-        <v>46263.7222853588</v>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="59" t="n">
-        <v>46263</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Q-26-003</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Not received</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>OUT   fill: Item  Out  Reason</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Mango Fas</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>3</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Customs</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-05-02-01-01</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O42" t="n">
-        <v>3</v>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Q-20260829-0004</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="R42" s="61" t="n">
-        <v>46263.72399579861</v>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="59" t="n">
-        <v>46263</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Q-26-003</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Scrap</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>OUT   fill: Item  Out  Reason</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Mango Owais</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>2</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>voided by admin 29 Aug 17:29</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-12-02-01-01</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O43" t="n">
-        <v>2</v>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Q-20260829-0005</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="R43" s="61" t="n">
-        <v>46263.72583758102</v>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="59" t="n">
-        <v>46263</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Q-26-003</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Scrap</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>OUT   fill: Item  Out  Reason</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Mango Owais</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>voided by admin 29 Aug 17:29</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-12-02-01-01</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O44" t="n">
-        <v>2</v>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Q-20260829-0006</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="R44" s="61" t="n">
-        <v>46263.72602355324</v>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="59" t="n">
-        <v>46263</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Q-26-003</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>To Courier</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OUT   fill: Item  Out  Courier  </t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Mango Owais</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>28</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>WareOne</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-12-02-01-01</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O45" t="n">
-        <v>28</v>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Q-20260829-0007</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="R45" s="61" t="n">
-        <v>46263.72928923611</v>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="59" t="n">
-        <v>46263</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Q-26-003</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Returned</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>IN   fill: Item  In  Courier  Reason</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Mango Owais</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>6</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>WareOne</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Customer Refused</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>voided by admin 29 Aug 17:32</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-12-02-01-01</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O46" t="n">
-        <v>6</v>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Q-20260829-0008</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="R46" s="61" t="n">
-        <v>46263.73066756944</v>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="59" t="n">
-        <v>46263</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Q-26-003</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Scrap</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>OUT   fill: Item  Out  Reason</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Mango Owais</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>2</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-12-02-01-01</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O47" t="n">
-        <v>2</v>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Q-20260829-0009</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="R47" s="61" t="n">
-        <v>46263.77142931713</v>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="59" t="n">
-        <v>46263</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Q-26-003</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Returned</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>IN   fill: Item  In  Courier  Reason</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Mango Owais</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>6</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>WareOne</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Customer Refused</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>voided by admin 29 Aug 18:36</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>EG-FG-MNG-12-02-01-01</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="O48" t="n">
-        <v>6</v>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Q-20260829-0010</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="R48" s="61" t="n">
-        <v>46263.7751134838</v>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
+    <row r="7" ht="15" customHeight="1" s="55"/>
+    <row r="8" ht="15" customHeight="1" s="55"/>
+    <row r="9" ht="15" customHeight="1" s="55"/>
+    <row r="10" ht="15" customHeight="1" s="55"/>
+    <row r="11" ht="15" customHeight="1" s="55"/>
+    <row r="12" ht="15" customHeight="1" s="55"/>
+    <row r="13" ht="15" customHeight="1" s="55"/>
+    <row r="14" ht="15" customHeight="1" s="55"/>
+    <row r="15" ht="15" customHeight="1" s="55"/>
+    <row r="16" ht="15" customHeight="1" s="55"/>
+    <row r="17" ht="15" customHeight="1" s="55"/>
+    <row r="18" ht="15" customHeight="1" s="55"/>
+    <row r="19" ht="15" customHeight="1" s="55"/>
+    <row r="20" ht="15" customHeight="1" s="55"/>
+    <row r="21" ht="15" customHeight="1" s="55"/>
+    <row r="22" ht="15" customHeight="1" s="55"/>
+    <row r="23" ht="15" customHeight="1" s="55"/>
+    <row r="24" ht="15" customHeight="1" s="55"/>
+    <row r="25" ht="15" customHeight="1" s="55"/>
+    <row r="26" ht="15" customHeight="1" s="55"/>
+    <row r="27" ht="15" customHeight="1" s="55"/>
+    <row r="28" ht="15" customHeight="1" s="55"/>
   </sheetData>
   <conditionalFormatting sqref="P7:P8561">
     <cfRule type="expression" priority="2" dxfId="0">
@@ -7224,7 +3798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="55" min="1" max="1"/>
@@ -7305,17 +3879,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="55">
-      <c r="A7" s="49" t="n"/>
-      <c r="B7" s="50" t="n"/>
-      <c r="C7" s="50" t="n"/>
-      <c r="D7" s="50" t="n"/>
-      <c r="E7" s="50" t="n"/>
-      <c r="F7" s="51" t="n"/>
-      <c r="G7" s="50" t="n"/>
-      <c r="H7" s="41" t="n"/>
-      <c r="I7" s="41" t="n"/>
-    </row>
+    <row r="7" ht="15" customHeight="1" s="55"/>
   </sheetData>
   <conditionalFormatting sqref="I7:I9000">
     <cfRule type="expression" priority="2" dxfId="0">
@@ -7484,13 +4048,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{659E6CF3-0F4A-409D-AD14-4AE7D4F368A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B49B2771-1988-4B3E-A8BC-F5BBF35B9DDD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E868B1FC-FDA7-4769-B050-5BF2503A6552}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AC40BED-4D94-43DF-AE3B-59A12FE7D057}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00243A3-8AF8-403A-8C03-4281C387CE91}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B35D5810-CB0B-423C-AABA-44927AEB8D16}"/>
 </file>
--- a/Stock_Control/INRIPE_Stock_Entry_v1.xlsx
+++ b/Stock_Control/INRIPE_Stock_Entry_v1.xlsx
@@ -225,7 +225,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -306,6 +306,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00152947"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -396,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -537,6 +542,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1056,14 +1064,14 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="tblItems" displayName="tblItems" ref="B15:D47" headerRowCount="1">
-  <autoFilter ref="B15:D47"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="tblItems" displayName="tblItems" ref="B15:D58" headerRowCount="1">
+  <autoFilter ref="B15:D58"/>
   <tableColumns count="3">
     <tableColumn id="2" name="Item Name"/>
     <tableColumn id="3" name="Item Code"/>
     <tableColumn id="4" name="Active"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
 </file>
 
@@ -1649,7 +1657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB47"/>
+  <dimension ref="A1:AB58"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" style="55" min="1" max="1"/>
@@ -3172,6 +3180,193 @@
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="64" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="C48" s="64" t="inlineStr">
+        <is>
+          <t>EG-FG-WTM-01-02-01-01</t>
+        </is>
+      </c>
+      <c r="D48" s="64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="64" t="inlineStr">
+        <is>
+          <t>Peach Sugary</t>
+        </is>
+      </c>
+      <c r="C49" s="64" t="inlineStr">
+        <is>
+          <t>EG-FG-PCH-01-02-01-01</t>
+        </is>
+      </c>
+      <c r="D49" s="64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="64" t="inlineStr">
+        <is>
+          <t>Apricot Amar</t>
+        </is>
+      </c>
+      <c r="C50" s="64" t="inlineStr">
+        <is>
+          <t>EG-FG-APR-01-02-01-01</t>
+        </is>
+      </c>
+      <c r="D50" s="64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="64" t="inlineStr">
+        <is>
+          <t>Peach Baladi</t>
+        </is>
+      </c>
+      <c r="C51" s="64" t="inlineStr">
+        <is>
+          <t>EG-FG-PCH-02-02-01-01</t>
+        </is>
+      </c>
+      <c r="D51" s="64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="64" t="inlineStr">
+        <is>
+          <t>Berries Omani</t>
+        </is>
+      </c>
+      <c r="C52" s="64" t="inlineStr">
+        <is>
+          <t>EG-FG-BER-01-02-01-01</t>
+        </is>
+      </c>
+      <c r="D52" s="64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="64" t="inlineStr">
+        <is>
+          <t>Grapes White</t>
+        </is>
+      </c>
+      <c r="C53" s="64" t="inlineStr">
+        <is>
+          <t>EG-FG-GRP-02-02-01-01</t>
+        </is>
+      </c>
+      <c r="D53" s="64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="64" t="inlineStr">
+        <is>
+          <t>Mango Timor Yemeni</t>
+        </is>
+      </c>
+      <c r="C54" s="64" t="inlineStr">
+        <is>
+          <t>EG-FG-MNG-16-01-01-01</t>
+        </is>
+      </c>
+      <c r="D54" s="64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="64" t="inlineStr">
+        <is>
+          <t>Plum Hollywood</t>
+        </is>
+      </c>
+      <c r="C55" s="64" t="inlineStr">
+        <is>
+          <t>EG-FG-PLM-01-02-01-01</t>
+        </is>
+      </c>
+      <c r="D55" s="64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="64" t="inlineStr">
+        <is>
+          <t>Golden Berry</t>
+        </is>
+      </c>
+      <c r="C56" s="64" t="inlineStr">
+        <is>
+          <t>EG-FG-GLD-01-02-01-01</t>
+        </is>
+      </c>
+      <c r="D56" s="64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="64" t="inlineStr">
+        <is>
+          <t>Bashmala</t>
+        </is>
+      </c>
+      <c r="C57" s="64" t="inlineStr">
+        <is>
+          <t>EG-FG-BSH-01-02-01-01</t>
+        </is>
+      </c>
+      <c r="D57" s="64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="64" t="inlineStr">
+        <is>
+          <t>Apple Baladi</t>
+        </is>
+      </c>
+      <c r="C58" s="64" t="inlineStr">
+        <is>
+          <t>EG-FG-APL-01-02-01-01</t>
+        </is>
+      </c>
+      <c r="D58" s="64" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4048,13 +4243,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B49B2771-1988-4B3E-A8BC-F5BBF35B9DDD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E851381-A0E2-40AA-A3AF-9A240AA726B1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AC40BED-4D94-43DF-AE3B-59A12FE7D057}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7BAD26A-5F61-4C15-9A21-64B892FD2FD8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B35D5810-CB0B-423C-AABA-44927AEB8D16}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C1512BA-E2FD-41F7-95A2-271EF61283A5}"/>
 </file>